--- a/ds-lab2/main/doc2vec_hyperparameter_comparison.xlsx
+++ b/ds-lab2/main/doc2vec_hyperparameter_comparison.xlsx
@@ -486,16 +486,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.3208775818347931</v>
+        <v>0.3199238777160645</v>
       </c>
       <c r="F2" t="n">
-        <v>0.778645396232605</v>
+        <v>0.808089554309845</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1811594202898551</v>
+        <v>0.192481884057971</v>
       </c>
       <c r="H2" t="n">
-        <v>3.884994268417358</v>
+        <v>4.454994678497314</v>
       </c>
     </row>
     <row r="3">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.320474237203598</v>
+        <v>0.3173440098762512</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7849185466766357</v>
+        <v>0.7859437465667725</v>
       </c>
       <c r="G3" t="n">
-        <v>0.192481884057971</v>
+        <v>0.2038043478260869</v>
       </c>
       <c r="H3" t="n">
-        <v>3.947012662887573</v>
+        <v>4.621001005172729</v>
       </c>
     </row>
     <row r="4">
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.323306679725647</v>
+        <v>0.316442459821701</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7788597941398621</v>
+        <v>0.8100631833076477</v>
       </c>
       <c r="G4" t="n">
-        <v>0.192481884057971</v>
+        <v>0.1471920289855073</v>
       </c>
       <c r="H4" t="n">
-        <v>3.828986644744873</v>
+        <v>3.789003610610962</v>
       </c>
     </row>
     <row r="5">
@@ -570,16 +570,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.320219874382019</v>
+        <v>0.3176172971725464</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7638829946517944</v>
+        <v>0.7833667397499084</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2151268115942029</v>
+        <v>0.192481884057971</v>
       </c>
       <c r="H5" t="n">
-        <v>4.401001930236816</v>
+        <v>3.100995779037476</v>
       </c>
     </row>
     <row r="6">
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.3210924565792084</v>
+        <v>0.3145055174827576</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7740117907524109</v>
+        <v>0.804193377494812</v>
       </c>
       <c r="G6" t="n">
         <v>0.1358695652173913</v>
       </c>
       <c r="H6" t="n">
-        <v>6.246001958847046</v>
+        <v>3.885003089904785</v>
       </c>
     </row>
     <row r="7">
@@ -626,16 +626,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.3205143809318542</v>
+        <v>0.3139104545116425</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7891064882278442</v>
+        <v>0.8096454739570618</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1471920289855073</v>
+        <v>0.1358695652173913</v>
       </c>
       <c r="H7" t="n">
-        <v>6.242002248764038</v>
+        <v>5.375848054885864</v>
       </c>
     </row>
     <row r="8">
@@ -654,16 +654,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.3212577998638153</v>
+        <v>0.3155374526977539</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7842351794242859</v>
+        <v>0.8160395622253418</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1019021739130435</v>
+        <v>0.1245471014492753</v>
       </c>
       <c r="H8" t="n">
-        <v>6.199998140335083</v>
+        <v>4.980412006378174</v>
       </c>
     </row>
     <row r="9">
@@ -682,16 +682,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.3204675614833832</v>
+        <v>0.315353125333786</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7870081663131714</v>
+        <v>0.8187257647514343</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09057971014492754</v>
+        <v>0.1471920289855073</v>
       </c>
       <c r="H9" t="n">
-        <v>6.484000205993652</v>
+        <v>5.363521337509155</v>
       </c>
     </row>
   </sheetData>

--- a/ds-lab2/main/doc2vec_hyperparameter_comparison.xlsx
+++ b/ds-lab2/main/doc2vec_hyperparameter_comparison.xlsx
@@ -486,16 +486,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.3199238777160645</v>
+        <v>0.3187263607978821</v>
       </c>
       <c r="F2" t="n">
-        <v>0.808089554309845</v>
+        <v>0.8130139708518982</v>
       </c>
       <c r="G2" t="n">
         <v>0.192481884057971</v>
       </c>
       <c r="H2" t="n">
-        <v>4.454994678497314</v>
+        <v>3.220001459121704</v>
       </c>
     </row>
     <row r="3">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3173440098762512</v>
+        <v>0.3190696239471436</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7859437465667725</v>
+        <v>0.8143627047538757</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2038043478260869</v>
+        <v>0.1698369565217391</v>
       </c>
       <c r="H3" t="n">
-        <v>4.621001005172729</v>
+        <v>2.981995582580566</v>
       </c>
     </row>
     <row r="4">
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.316442459821701</v>
+        <v>0.316289484500885</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8100631833076477</v>
+        <v>0.7986841797828674</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1471920289855073</v>
+        <v>0.2038043478260869</v>
       </c>
       <c r="H4" t="n">
-        <v>3.789003610610962</v>
+        <v>2.749002695083618</v>
       </c>
     </row>
     <row r="5">
@@ -570,16 +570,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.3176172971725464</v>
+        <v>0.3174415230751038</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7833667397499084</v>
+        <v>0.7952873706817627</v>
       </c>
       <c r="G5" t="n">
-        <v>0.192481884057971</v>
+        <v>0.1698369565217391</v>
       </c>
       <c r="H5" t="n">
-        <v>3.100995779037476</v>
+        <v>2.871002435684204</v>
       </c>
     </row>
     <row r="6">
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.3145055174827576</v>
+        <v>0.3157826960086823</v>
       </c>
       <c r="F6" t="n">
-        <v>0.804193377494812</v>
+        <v>0.8193150162696838</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1358695652173913</v>
+        <v>0.1471920289855073</v>
       </c>
       <c r="H6" t="n">
-        <v>3.885003089904785</v>
+        <v>3.728999376296997</v>
       </c>
     </row>
     <row r="7">
@@ -626,16 +626,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.3139104545116425</v>
+        <v>0.3154133856296539</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8096454739570618</v>
+        <v>0.8192870020866394</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1358695652173913</v>
+        <v>0.1245471014492753</v>
       </c>
       <c r="H7" t="n">
-        <v>5.375848054885864</v>
+        <v>3.660001277923584</v>
       </c>
     </row>
     <row r="8">
@@ -654,16 +654,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.3155374526977539</v>
+        <v>0.3162590265274048</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8160395622253418</v>
+        <v>0.8155057430267334</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1245471014492753</v>
+        <v>0.1132246376811594</v>
       </c>
       <c r="H8" t="n">
-        <v>4.980412006378174</v>
+        <v>3.944996118545532</v>
       </c>
     </row>
     <row r="9">
@@ -682,16 +682,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.315353125333786</v>
+        <v>0.3157591819763184</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8187257647514343</v>
+        <v>0.8173186182975769</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1471920289855073</v>
+        <v>0.09057971014492754</v>
       </c>
       <c r="H9" t="n">
-        <v>5.363521337509155</v>
+        <v>3.834000825881958</v>
       </c>
     </row>
   </sheetData>
